--- a/AI_AuditLog_DoanNhat.xlsx
+++ b/AI_AuditLog_DoanNhat.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Semester 5\SWR302\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Semester 5\SWR302\ai-audit-log-DoanNhat219\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0727D52-9C64-49DB-A994-0C1190F5B5D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{132C6AD1-E127-4E4A-A76A-E32637E311B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="16090" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="16090" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="175">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -469,6 +469,96 @@
   </si>
   <si>
     <t>Viết lại logic hoàn tiền trong Decision Tree, bổ sung ràng buộc nghiêm ngặt về % tiến độ khóa học đã xem.</t>
+  </si>
+  <si>
+    <t>Phân rã luồng giao tiếp giữa các đối tượng (objects) khi học viên thực hiện chức năng "Nộp bài tập" (Submit Assignment).</t>
+  </si>
+  <si>
+    <t>"Viết luồng các bước chi tiết cho Sequence Diagram chức năng 'Submit Assignment' trên EduDesk."</t>
+  </si>
+  <si>
+    <t>AI liệt kê luồng cơ bản: Student -&gt; UI -&gt; Controller -&gt; Database. Sinh viên upload file, hệ thống lưu và báo thành công.</t>
+  </si>
+  <si>
+    <t>AI bỏ quên yếu tố kiểm duyệt (Validation) đối với file tải lên. Tôi đã tự cấu trúc lại luồng bằng cách chèn thêm bước Validate tại Controller. Nếu file &gt; 50MB hoặc sai định dạng (không phải PDF/DOCX), Controller sẽ trả về lỗi ngay lập tức mà không gọi xuống Database. Điều này giúp tối ưu luồng xử lý và sát thực tế.</t>
+  </si>
+  <si>
+    <t>Biểu đồ Sequence Diagram cho chức năng "Submit Assignment".</t>
+  </si>
+  <si>
+    <t>Xác định các yêu cầu phi chức năng (Non-functional requirements - NFRs) về bảo mật và hiệu năng cho EduDesk.</t>
+  </si>
+  <si>
+    <t>"Liệt kê các Non-functional requirements (NFRs) quan trọng nhất cho một nền tảng học trực tuyến có streaming video."</t>
+  </si>
+  <si>
+    <t>AI đưa ra các NFRs chung chung: Hệ thống phải nhanh, bảo mật mật khẩu, hỗ trợ nhiều người dùng cùng lúc.</t>
+  </si>
+  <si>
+    <t>Các NFRs AI gợi ý thiếu tính đo lường (Measurability). Tôi đã vận dụng tiêu chuẩn SMART để viết lại. Ví dụ: Thay vì "hệ thống phải nhanh", tôi đổi thành "Video player phải load xong buffer trong &lt; 3 giây ở mạng 4G". Tôi cũng tự bổ sung NFR về việc tuân thủ chuẩn PCI DSS vì EduDesk có cổng thanh toán.</t>
+  </si>
+  <si>
+    <t>Tài liệu SRS (Software Requirements Specification) - phần Non-functional Requirements.</t>
+  </si>
+  <si>
+    <t>Khái quát hóa các thuộc tính (attributes) và quan hệ cho thực thể User trong hệ thống để vẽ Class Diagram.</t>
+  </si>
+  <si>
+    <t>"Xây dựng mô hình Class Diagram cho đối tượng User trong nền tảng học tập, áp dụng tính kế thừa (inheritance)."</t>
+  </si>
+  <si>
+    <t>AI tạo class User cha, và các class con Student, Instructor kế thừa toàn bộ thuộc tính của cha.</t>
+  </si>
+  <si>
+    <t>Cách thiết kế kế thừa của AI gây rủi ro nếu một người dùng vừa là Instructor vừa là Student. Thay vì làm theo AI, tôi đã tư duy lại và thiết kế theo cơ chế Role-based (RBAC). Class "User" đứng độc lập và liên kết 1-nhiều với class "Role". Cách đóng gói trừu tượng này giúp cơ sở dữ liệu sau này dễ dàng mở rộng hơn.</t>
+  </si>
+  <si>
+    <t>Biểu đồ Class Diagram (Domain Model).</t>
+  </si>
+  <si>
+    <t>Omission</t>
+  </si>
+  <si>
+    <t>Structural Flaw</t>
+  </si>
+  <si>
+    <t>Khi tạo luồng Sequence Diagram cho chức năng nộp bài (Submit Assignment), AI mặc định luồng đi thẳng từ UI qua Controller và lưu trực tiếp xuống Database.</t>
+  </si>
+  <si>
+    <t>Khi thiết kế Class Diagram, AI khẳng định nên dùng tính Kế thừa (Inheritance): class Student và Instructor kế thừa trực tiếp từ class User cha.</t>
+  </si>
+  <si>
+    <t>Hệ thống thực tế bắt buộc phải có bước Validation (kiểm tra dung lượng tối đa, định dạng file hợp lệ) tại Controller trước khi lưu trữ để tránh treo server hoặc lỗi bảo mật.</t>
+  </si>
+  <si>
+    <t>vTrong thực tế nền tảng EduDesk, một người dùng có thể đóng nhiều vai trò (vừa là Instructor tạo khóa học, vừa mua khóa khác để học với vai trò Student). Kế thừa cứng sẽ không xử lý được.</t>
+  </si>
+  <si>
+    <t>Kiểm tra đối chiếu với các nguyên tắc bảo mật và System Architecture cơ bản cho hệ thống Web.</t>
+  </si>
+  <si>
+    <t>Phân tích Domain Model và các ràng buộc về Multi-role (Đa vai trò) thường thấy ở hệ thống E-learning.</t>
+  </si>
+  <si>
+    <t>Bổ sung khối "Validate File" trong biểu đồ. Rẽ nhánh Alt (Alternative): Nếu file lỗi, trả về "Error Message" ngay lập tức mà không gọi xuống Database.</t>
+  </si>
+  <si>
+    <t>Bác bỏ mô hình AI gợi ý. Thiết kế lại theo hướng Role-Based (RBAC): tách class Role riêng biệt và tạo quan hệ Association (1-nhiều) với class User.</t>
+  </si>
+  <si>
+    <t>Dangerous Assumption</t>
+  </si>
+  <si>
+    <t>AI gợi ý thao tác "Delete" (Xóa bản ghi trực tiếp) cho chức năng xóa tài khoản người dùng khỏi hệ thống.</t>
+  </si>
+  <si>
+    <t>Việc xóa vĩnh viễn (Hard Delete) người dùng trên nền tảng có giao dịch tài chính (mua/bán khóa học) sẽ làm hỏng dữ liệu liên kết ở bảng Hóa đơn (Invoices) và Lịch sử học (Enrollments).</t>
+  </si>
+  <si>
+    <t>Kiểm tra đối chiếu với nguyên tắc thiết kế Cơ sở dữ liệu quan hệ (Database Referential Integrity) và ràng buộc về kế toán.</t>
+  </si>
+  <si>
+    <t>Thay thế "Delete" bằng "Deactivate/Soft Delete". Thêm trường is_active (boolean) vào bảng User trong Database Schema để chỉ ẩn tài khoản thay vì xóa hẳn.</t>
   </si>
 </sst>
 </file>
@@ -645,10 +735,16 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -657,12 +753,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -977,14 +1067,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
     </row>
     <row r="3" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
@@ -1207,28 +1297,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
@@ -1260,7 +1350,7 @@
       <c r="A4" s="7">
         <v>1</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="18" t="s">
         <v>115</v>
       </c>
       <c r="C4" s="7" t="s">
@@ -1359,34 +1449,82 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
+      <c r="A8" s="7">
+        <v>5</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="9" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
+      <c r="A9" s="7">
+        <v>6</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="10" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
+      <c r="A10" s="7">
+        <v>7</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="11" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="7"/>
@@ -1527,28 +1665,28 @@
     <col min="3" max="3" width="42.81640625" customWidth="1"/>
     <col min="4" max="4" width="52.81640625" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="33.36328125" customWidth="1"/>
+    <col min="6" max="6" width="37.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
     </row>
     <row r="3" spans="1:6" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
@@ -1611,28 +1749,64 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
+      <c r="A6" s="7">
+        <v>3</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
+      <c r="A7" s="7">
+        <v>4</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
+      <c r="A8" s="7">
+        <v>5</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="7"/>
@@ -1830,20 +2004,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
     </row>
     <row r="4" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">

--- a/AI_AuditLog_DoanNhat.xlsx
+++ b/AI_AuditLog_DoanNhat.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Semester 5\SWR302\ai-audit-log-DoanNhat219\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{132C6AD1-E127-4E4A-A76A-E32637E311B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB3968A-415E-4E2E-B43A-26CD5662BBFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="16090" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="16090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="202">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -375,9 +375,6 @@
     <t>SWR302</t>
   </si>
   <si>
-    <t>EduDesk</t>
-  </si>
-  <si>
     <t>Gemini</t>
   </si>
   <si>
@@ -559,6 +556,90 @@
   </si>
   <si>
     <t>Thay thế "Delete" bằng "Deactivate/Soft Delete". Thêm trường is_active (boolean) vào bảng User trong Database Schema để chỉ ẩn tài khoản thay vì xóa hẳn.</t>
+  </si>
+  <si>
+    <t>Xác định các yêu cầu phi chức năng (Non-functional requirements - NFRs) về bảo mật và hiệu năng cho hệ thống HRP.</t>
+  </si>
+  <si>
+    <t>"Liệt kê các Non-functional requirements quan trọng nhất cho một nền tảng học trực tuyến có video bài giảng."</t>
+  </si>
+  <si>
+    <t>Các NFRs AI gợi ý thiếu tính đo lường (Measurability). Tôi đã vận dụng tiêu chuẩn SMART để viết lại. Ví dụ: "Video player phải load xong buffer trong &lt; 3 giây ở mạng 4G" và bổ sung NFR về việc tuân thủ chuẩn bảo mật OWASP.</t>
+  </si>
+  <si>
+    <t>Abstraction / Use Case Modeling</t>
+  </si>
+  <si>
+    <t>Băn khoăn về quy trình chuẩn bị trước khi vẽ các biểu đồ luồng nghiệp vụ chi tiết như Swimlane.</t>
+  </si>
+  <si>
+    <t>AI xác nhận là rất cần thiết, vì Use Case là "xương sống", giúp kiểm tra chéo (cross-check) Context Diagram và là tiền đề vẽ Swimlane Diagram.</t>
+  </si>
+  <si>
+    <t>Dù đề bài (phần 6) không bắt buộc nộp Use Case Diagram, tôi đã quyết định TỰ XÂY DỰNG danh sách các Use Case làm kim chỉ nam. Nhờ vậy, khi chuyển sang vẽ Swimlane, tôi phân định rõ ràng ranh giới trách nhiệm của từng Actor (Lanes) thay vì vẽ theo cảm tính.</t>
+  </si>
+  <si>
+    <t>Danh sách Use Case nháp.</t>
+  </si>
+  <si>
+    <t>Verification/Review</t>
+  </si>
+  <si>
+    <t>Workflow Design / Swimlane Diagram</t>
+  </si>
+  <si>
+    <t>Cần kiểm tra lại độ chính xác của bản vẽ Swimlane Diagram và hiểu rõ luồng nghiệp vụ hệ thống để chuẩn bị thi vấn đáp.</t>
+  </si>
+  <si>
+    <t>[Tải lên hình ảnh bản vẽ Swimlane] giải thích các luoogf đi mai tôi kiểm tra bạn"</t>
+  </si>
+  <si>
+    <t>AI phân tích và chia bản vẽ thành 4 module chính (Setup, Booking/Pricing, Payment, Cancellation) và đánh giá cao các nút rẽ nhánh (Decision nodes) xử lý Business Rules.</t>
+  </si>
+  <si>
+    <t>Bản vẽ Swimlane hoàn thiện.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oversimplification / Logic Omission </t>
+  </si>
+  <si>
+    <t>Ở các bước phân tích ban đầu, khi bóc tách text của đề bài, các hành động thường được liệt kê theo một đường thẳng (Happy path): "User searches space -&gt; books -&gt; pays -&gt; System processes".</t>
+  </si>
+  <si>
+    <t>Theo quy trình nghiệp vụ (Business Rules) thực tế của một hệ thống Booking, quá trình thanh toán qua cổng thứ 3 (Payment Gateway) không bao giờ thành công 100%. Nếu chỉ đi theo 1 luồng thẳng, hệ thống sẽ bị "treo" khi khách hàng thanh toán lỗi.</t>
+  </si>
+  <si>
+    <t>p dụng tư duy phản biện (Critical Thinking) và kinh nghiệm thiết kế quy trình thực tế.</t>
+  </si>
+  <si>
+    <t>Tôi đã TỰ BỔ SUNG vòng lặp kiểm tra "Payment successful?" và nhánh rẽ "Retry payment" vào bản vẽ Swimlane Diagram thực tế của mình (điều mà text đề bài không ghi rõ). Đồng thời bổ sung các nhánh kiểm duyệt của Admin để đảm bảo chặt chẽ.</t>
+  </si>
+  <si>
+    <t>Khi được yêu cầu tư vấn các thực thể cho Context Diagram, AI chỉ liệt kê User, Admin, Space Manager và Payment System. Nó mặc định chức năng đăng nhập là nội bộ (Local Login) do Hệ thống tự xử lý.</t>
+  </si>
+  <si>
+    <t>Theo tài liệu dự án, có yêu cầu rõ ràng: "Google login is supported" và "ensures only verified users can access sensitive info". Việc AI bỏ qua chi tiết này dẫn đến thiếu mất một hệ thống bên ngoài rất quan trọng là nền tảng xác thực của Google.</t>
+  </si>
+  <si>
+    <t>Rà soát lại từng câu chữ trong đoạn mô tả requirement tổng quan và đối chiếu với bản vẽ do AI gợi ý.</t>
+  </si>
+  <si>
+    <t>Tôi đã TỰ BỔ SUNG thêm "Google Identity System" (hoặc Google OAuth API) làm một External Entity (Thực thể bên ngoài) trong tài liệu phân tích và bổ sung luồng Login Auth vào sơ đồ.</t>
+  </si>
+  <si>
+    <t>Khi gợi ý vẽ State Diagram (Biểu đồ trạng thái) cho đối tượng Reservation (Đơn đặt chỗ), AI đưa ra một luồng tuyến tính: Requested -&gt; Paid -&gt; Confirmed -&gt; Cancelled, và kết thúc luồng hủy tại đó.</t>
+  </si>
+  <si>
+    <t>Đề bài quy định rõ Business Rule: "Cancellations made 12 hours prior are refundable". Trạng thái "Cancelled" chung chung không thể hiện được việc đơn hàng đó có được hoàn tiền hay không. Về mặt hệ thống kế toán, một đơn "Hủy có hoàn tiền" khác hoàn toàn với "Hủy mất tiền".</t>
+  </si>
+  <si>
+    <t>Áp dụng kiến thức học trong môn SWR302 về việc phải làm rõ các trạng thái dữ liệu (Data States) dựa trên các ràng buộc nghiệp vụ (Business Rules).</t>
+  </si>
+  <si>
+    <t>Tôi đã chỉnh sửa lại bản vẽ State Diagram, tách trạng thái sau khi hủy thành nhánh điều kiện: Nếu hủy trước 12h -&gt; chuyển sang trạng thái "Refunded" (Đã hoàn tiền). Nếu hủy sau 12h -&gt; chuyển sang trạng thái "Cancelled" (Đã hủy - Không hoàn tiền).</t>
+  </si>
+  <si>
+    <t>HRP</t>
   </si>
 </sst>
 </file>
@@ -738,20 +819,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1067,7 +1148,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="20"/>
@@ -1110,7 +1191,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>113</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -1207,7 +1288,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -1297,7 +1378,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="21" t="s">
         <v>37</v>
       </c>
       <c r="B1" s="20"/>
@@ -1309,7 +1390,7 @@
       <c r="H1" s="20"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="19" t="s">
         <v>38</v>
       </c>
       <c r="B2" s="20"/>
@@ -1351,25 +1432,25 @@
         <v>1</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>32</v>
       </c>
       <c r="D4" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="H4" s="7" t="s">
         <v>119</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.35">
@@ -1377,22 +1458,22 @@
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>35</v>
       </c>
       <c r="D5" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="G5" s="7" t="s">
         <v>124</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>125</v>
       </c>
       <c r="H5" s="7"/>
     </row>
@@ -1401,25 +1482,25 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>34</v>
       </c>
       <c r="D6" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="F6" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="G6" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="H6" s="7" t="s">
         <v>133</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.35">
@@ -1427,25 +1508,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>36</v>
       </c>
       <c r="D7" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="F7" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="G7" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="H7" s="7" t="s">
         <v>139</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.35">
@@ -1453,25 +1534,25 @@
         <v>5</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>32</v>
       </c>
       <c r="D8" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="F8" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="G8" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="H8" s="7" t="s">
         <v>148</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.35">
@@ -1479,25 +1560,25 @@
         <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>34</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="F9" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="G9" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="H9" s="7" t="s">
         <v>153</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.35">
@@ -1505,56 +1586,104 @@
         <v>7</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>35</v>
       </c>
       <c r="D10" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="F10" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="G10" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="H10" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="H10" s="7" t="s">
-        <v>159</v>
-      </c>
     </row>
     <row r="11" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
+      <c r="A11" s="7">
+        <v>8</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="12" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
+      <c r="A12" s="7">
+        <v>9</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="13" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
+      <c r="A13" s="7">
+        <v>10</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="14" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="7"/>
@@ -1662,14 +1791,14 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="42.81640625" customWidth="1"/>
-    <col min="4" max="4" width="52.81640625" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="37.36328125" customWidth="1"/>
+    <col min="3" max="3" width="50.453125" customWidth="1"/>
+    <col min="4" max="4" width="68.36328125" customWidth="1"/>
+    <col min="5" max="5" width="38.36328125" customWidth="1"/>
+    <col min="6" max="6" width="66" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>50</v>
       </c>
       <c r="B1" s="20"/>
@@ -1679,7 +1808,7 @@
       <c r="F1" s="20"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="22" t="s">
         <v>51</v>
       </c>
       <c r="B2" s="20"/>
@@ -1716,16 +1845,16 @@
         <v>65</v>
       </c>
       <c r="C4" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>128</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
@@ -1736,16 +1865,16 @@
         <v>68</v>
       </c>
       <c r="C5" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>143</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
@@ -1753,19 +1882,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
@@ -1773,19 +1902,19 @@
         <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
@@ -1793,44 +1922,80 @@
         <v>5</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="D8" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="E8" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="F8" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>174</v>
-      </c>
     </row>
     <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
+      <c r="A9" s="7">
+        <v>6</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="10" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
+      <c r="A10" s="7">
+        <v>7</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="11" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
+      <c r="A11" s="7">
+        <v>8</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="12" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="7"/>
@@ -2004,7 +2169,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="21" t="s">
         <v>77</v>
       </c>
       <c r="B1" s="20"/>
@@ -2012,7 +2177,7 @@
       <c r="D1" s="20"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="24" t="s">
         <v>78</v>
       </c>
       <c r="B2" s="20"/>

--- a/AI_AuditLog_DoanNhat.xlsx
+++ b/AI_AuditLog_DoanNhat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Semester 5\SWR302\ai-audit-log-DoanNhat219\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB3968A-415E-4E2E-B43A-26CD5662BBFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819CFF0F-98CF-4D31-B6C9-46F1BD8A8691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="16090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="16090" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="242">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -640,6 +640,126 @@
   </si>
   <si>
     <t>HRP</t>
+  </si>
+  <si>
+    <t>Decomposition (Phân rã hệ thống)</t>
+  </si>
+  <si>
+    <t>Xây dựng luồng xử lý dữ liệu cho chức năng vô hiệu hóa nhân sự (UC-06: Deactivate Employee) khi có nhân sự nghỉ việc.</t>
+  </si>
+  <si>
+    <t>"Viết luồng xử lý và lệnh thao tác database bằng MongoDB để xóa một nhân sự khỏi hệ thống HRS khi HR Manager nhấn nút Deactivate."</t>
+  </si>
+  <si>
+    <t>AI đề xuất luồng xóa trực tiếp bằng lệnh db.employees.deleteOne({ _id: employeeId }) để giải phóng dung lượng và ghi log thao tác vào bảng ActivityLog.</t>
+  </si>
+  <si>
+    <t>Lời khuyên của AI mang rủi ro nghiêm trọng về mất mát dữ liệu. Dựa trên quy tắc nghiệp vụ BR-UC06-01 (Soft Delete Only), tôi đã BÁC BỎ hoàn toàn việc xóa cứng (hard-delete). Tôi tự thiết kế lại luồng: thay vì xóa, hệ thống sẽ gọi hàm cập nhật trạng thái status: 'Inactive', lưu lại end_date, và ngay lập tức gọi thêm một service để hủy toàn bộ phiên đăng nhập hiện tại của nhân sự đó (BR-UC06-02). Việc này giúp bảo toàn được lịch sử điểm danh và bảng lương của họ.</t>
+  </si>
+  <si>
+    <t>Đoạn code xử lý logic hàm Deactivate trong controller/service.</t>
+  </si>
+  <si>
+    <t>Database Operations</t>
+  </si>
+  <si>
+    <t>Viết câu lệnh truy vấn MongoDB cho màn hình Danh sách nhân sự (Employee List) phục vụ việc hiển thị, phân trang và tìm kiếm.</t>
+  </si>
+  <si>
+    <t>Viết câu lệnh query MongoDB để lấy danh sách nhân viên cho màn hình Admin, có hỗ trợ tìm kiếm text."</t>
+  </si>
+  <si>
+    <t>AI cung cấp câu lệnh cơ bản sử dụng text index: db.employees.find({ $text: { $search: keyword } }).</t>
+  </si>
+  <si>
+    <t>Lệnh của AI không đáp ứng được yêu cầu bộ lọc nâng cao trên UI. Tôi đã tự cấu trúc lại câu query, sử dụng toán tử $or kết hợp với Regular Expression ($regex) để tìm kiếm đồng thời trên các trường fullName, email, và username không phân biệt chữ hoa chữ thường. Tôi cũng bổ sung thêm bộ lọc trạng thái (status), loại nhân sự (employeeType) và logic phân trang (skip, limit) đúng chuẩn thiết kế hệ thống.</t>
+  </si>
+  <si>
+    <t>Lệnh truy vấn MongoDB trong phần Database Access của UC-07 (View All Employees).</t>
+  </si>
+  <si>
+    <t>Requirement Analysis / Security</t>
+  </si>
+  <si>
+    <t>Xây dựng luồng tương tác (Sequence/Flow) cho tính năng Agent Support (UC-52) - AI nội bộ hỗ trợ nhân viên.</t>
+  </si>
+  <si>
+    <t>"Xây dựng luồng xử lý khi một nhân viên nhập lệnh (command) vào Agent Chat Interface để yêu cầu hệ thống thực hiện một tác vụ."</t>
+  </si>
+  <si>
+    <t>AI vẽ ra một luồng tuyến tính: User nhập lệnh -&gt; Agent tiếp nhận -&gt; Agent phân tích NLP -&gt; Gọi module tương ứng -&gt; Trả kết quả về cho user.</t>
+  </si>
+  <si>
+    <t>AI đã bỏ qua khía cạnh bảo mật và kiểm soát quyền. Tôi nhận diện được rủi ro leo thang đặc quyền (Privilege Escalation). Tuân thủ quy tắc BR-AGENT-01, tôi ĐÃ TỰ CHÈN THÊM bước "Authorization By User Credentials" vào giữa khâu tiếp nhận và khâu xử lý. Tác vụ chỉ được tiếp tục nếu Agent xác thực được người dùng có quyền (Role Permission) thực thi tính năng đó (ví dụ: Nhân viên không thể nhờ Agent sửa lương của người khác).</t>
+  </si>
+  <si>
+    <t>Sơ đồ Use Case và luồng xử lý UC-52 / UC-53 trong tài liệu.</t>
+  </si>
+  <si>
+    <t>Logic Design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Algorithms </t>
+  </si>
+  <si>
+    <t>Thiết kế logic tự động sinh bảng lương (Auto Payroll Generation) chạy ngầm (Cron Job) mỗi tháng.</t>
+  </si>
+  <si>
+    <t>"Viết thuật toán xử lý tính lương tự động hàng tháng cho nhân viên."</t>
+  </si>
+  <si>
+    <t>AI gợi ý thuật toán quét toàn bộ bảng Employee, lấy mức lương cơ bản nhân với số ngày làm việc chuẩn trong tháng rồi tạo record trong bảng Payroll.</t>
+  </si>
+  <si>
+    <t>Logic của AI quá lỏng lẻo. Quá trình làm việc nhóm cho thấy cần phải tích hợp dữ liệu từ module điểm danh. Tôi đã thiết kế lại thuật toán một cách toàn diện: (1) Chỉ quét các nhân sự đang Active hoặc vừa Inactive trong tháng hiện tại; (2) Kết nối chéo với bảng Attendance để đếm số lần quét vân tay thành công; (3) Cộng trừ các ngày nghỉ dựa trên các ApplicationForm có status = 'Approved'.</t>
+  </si>
+  <si>
+    <t>Mô tả logic tính lương trong module hrp.payroll.</t>
+  </si>
+  <si>
+    <t>Business Rule Violation / Data Integrity Risk</t>
+  </si>
+  <si>
+    <t>AI mặc định tư vấn sử dụng lệnh db.employees.deleteOne() hoặc findByIdAndDelete() của MongoDB để xử lý chức năng Deactivate Employee nhằm tối ưu cơ sở dữ liệu.</t>
+  </si>
+  <si>
+    <t>Hệ thống HRS chứa dữ liệu nhân sự liên kết chặt chẽ với lịch sử điểm danh (Attendance), bảng lương (Payroll), và công việc dự án (Task). Nếu nghe theo AI xóa cứng dữ liệu, hệ thống sẽ gặp lỗi mồ côi dữ liệu (orphan records) ở hàng loạt bảng khác, làm hỏng toàn bộ báo cáo kế toán và lịch sử dự án.</t>
+  </si>
+  <si>
+    <t>Đối chiếu logic của AI với ràng buộc hệ thống số BR-UC06-01 (Soft Delete Only) và quy tắc thiết kế Database chung của các nền tảng ERP/HRM.</t>
+  </si>
+  <si>
+    <t>Loại bỏ hoàn toàn gợi ý xóa của AI. Triển khai lệnh db.employees.findByIdAndUpdate() để thay đổi thuộc tính status thành Inactive thay vì xóa khỏi hệ thống.</t>
+  </si>
+  <si>
+    <t>Missing Constraint / Security Vulnerability</t>
+  </si>
+  <si>
+    <t>Khi được yêu cầu viết logic backend cho chức năng đăng nhập (Login System), AI chỉ cung cấp luồng xác thực cơ bản: Tìm User trong database -&gt; So sánh mật khẩu băm -&gt; Trả về token đăng nhập thành công hoặc thông báo lỗi nếu sai.</t>
+  </si>
+  <si>
+    <t>Code do AI sinh ra hoàn toàn cho phép hacker thử sai mật khẩu liên tục (Brute-force attack). Theo tài liệu thiết kế hệ thống, quy tắc nghiệp vụ FR3 (Account Locking) quy định rõ: Nếu người dùng nhập sai thông tin đăng nhập 6 lần liên tiếp, tài khoản phải bị khóa trong 30 phút. AI đã hoàn toàn "quên" mất logic bảo mật quan trọng này</t>
+  </si>
+  <si>
+    <t>Đối chiếu logic code do AI tạo ra với danh sách Business Rules của chức năng Authentication</t>
+  </si>
+  <si>
+    <t>Tôi đã BÁC BỎ code cũ và tự bổ sung thêm trường failedLoginAttempts và lockUntil vào schema của collection User trên MongoDB, đồng thời viết thêm logic: Cứ mỗi lần sai mật khẩu thì tăng biến đếm, nếu đạt mức 6 lần thì cập nhật thời gian khóa tài khoản thêm 30 phút.</t>
+  </si>
+  <si>
+    <t>Business Logic Error</t>
+  </si>
+  <si>
+    <t>Khi được yêu cầu thiết kế luồng trạng thái cho một Application Form (Nghỉ phép/Làm remote), AI đề xuất rằng sau khi nhân viên Submit, hệ thống sẽ tự động gán thẳng đơn đó cho HR Manager để duyệt nhằm "tối ưu hóa và rút ngắn quy trình".</t>
+  </si>
+  <si>
+    <t>Lời khuyên này đi ngược lại hoàn toàn với cấu trúc quản lý của công ty. Quy tắc BR-ATT-02 (Approval Hierarchy) quy định rất chặt chẽ: Các biểu mẫu đăng ký phải được xem xét bởi Team Leader trước tiên; đơn chỉ được chuyển thẳng lên HR Manager nếu nhân viên đó không thuộc team nào (không có Team Leader). Việc AI "tự tiện" rút ngắn quy trình sẽ làm hỏng hệ thống phân quyền của hệ thống.</t>
+  </si>
+  <si>
+    <t>Review lại luồng trạng thái (State workflow) của biểu mẫu và đối chiếu với quy tắc phân quyền (Authorization) trong tài liệu RDS</t>
+  </si>
+  <si>
+    <t>Tôi đã sửa lại thuật toán định tuyến đơn (Routing Logic): Hệ thống phải check xem teamLeaderId của nhân viên đó có tồn tại hay không. Nếu có -&gt; Noti cho Team Leader duyệt. Nếu null -&gt; Noti cho HR Manager.</t>
   </si>
 </sst>
 </file>
@@ -819,12 +939,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1148,7 +1268,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="20"/>
@@ -1370,15 +1490,15 @@
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="20.6328125" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="4" max="4" width="29.1796875" customWidth="1"/>
     <col min="5" max="5" width="32.6328125" customWidth="1"/>
     <col min="6" max="6" width="35" customWidth="1"/>
-    <col min="7" max="7" width="74.54296875" customWidth="1"/>
+    <col min="7" max="7" width="84.6328125" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="19" t="s">
         <v>37</v>
       </c>
       <c r="B1" s="20"/>
@@ -1390,7 +1510,7 @@
       <c r="H1" s="20"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="21" t="s">
         <v>38</v>
       </c>
       <c r="B2" s="20"/>
@@ -1686,44 +1806,108 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
+      <c r="A14" s="7">
+        <v>11</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="15" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
+      <c r="A15" s="7">
+        <v>12</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="16" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
+      <c r="A16" s="7">
+        <v>13</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>219</v>
+      </c>
     </row>
     <row r="17" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
+      <c r="A17" s="7">
+        <v>14</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="18" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="7"/>
@@ -1791,8 +1975,8 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="50.453125" customWidth="1"/>
-    <col min="4" max="4" width="68.36328125" customWidth="1"/>
+    <col min="3" max="3" width="53.453125" customWidth="1"/>
+    <col min="4" max="4" width="84.453125" customWidth="1"/>
     <col min="5" max="5" width="38.36328125" customWidth="1"/>
     <col min="6" max="6" width="66" customWidth="1"/>
   </cols>
@@ -1998,28 +2182,64 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
+      <c r="A12" s="7">
+        <v>9</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>231</v>
+      </c>
     </row>
     <row r="13" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
+      <c r="A13" s="7">
+        <v>10</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="14" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
+      <c r="A14" s="7">
+        <v>11</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="15" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="7"/>
@@ -2169,7 +2389,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="19" t="s">
         <v>77</v>
       </c>
       <c r="B1" s="20"/>

--- a/AI_AuditLog_DoanNhat.xlsx
+++ b/AI_AuditLog_DoanNhat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Semester 5\SWR302\ai-audit-log-DoanNhat219\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819CFF0F-98CF-4D31-B6C9-46F1BD8A8691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA95F311-9E26-4C16-B3C9-338F938F9FA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="16090" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="16090" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="282">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -760,6 +760,126 @@
   </si>
   <si>
     <t>Tôi đã sửa lại thuật toán định tuyến đơn (Routing Logic): Hệ thống phải check xem teamLeaderId của nhân viên đó có tồn tại hay không. Nếu có -&gt; Noti cho Team Leader duyệt. Nếu null -&gt; Noti cho HR Manager.</t>
+  </si>
+  <si>
+    <t>Omission / Missing Constraint</t>
+  </si>
+  <si>
+    <t>Khi yêu cầu tạo Acceptance Criteria (AC) cho chức năng "Đặt lịch khám", AI chỉ liệt kê các luồng cơ bản (Happy path) và bỏ trống dữ liệu, mặc định quên mất luồng xử lý đồng thời (Race condition) của nhiều bệnh nhân.</t>
+  </si>
+  <si>
+    <t>Trong thực tế vận hành hệ thống đặt lịch, tình huống 2 bệnh nhân cùng lúc click chọn khung giờ cuối cùng (chỉ còn 1 chỗ trống) rất dễ xảy ra và bắt buộc phải có AC để kiểm soát (Overbooking).</t>
+  </si>
+  <si>
+    <t>Đối chiếu với kiến thức về "Edge Cases" trong kiểm thử hệ thống và đặt câu hỏi phản biện: "Điều gì xảy ra nếu 2 user thao tác cùng đúng một giây?".</t>
+  </si>
+  <si>
+    <t>Tôi đã tự bổ sung thêm AC thứ 5 chuyên xử lý "Race Condition" vào bài làm: Yêu cầu hệ thống phải ưu tiên request đến trước (hoặc lock database) và báo lỗi hết chỗ cho người đến sau.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oversimplification </t>
+  </si>
+  <si>
+    <t>Ở câu 1c (Deadline rút ngắn còn 5 tuần), AI cho rằng vẫn có thể giữ lại yêu cầu "Gửi SMS tự động" (R03) vì logic code để gọi hàm gửi tin nhắn rất đơn giản và nhanh.</t>
+  </si>
+  <si>
+    <t>Quy trình thực tế để tích hợp SMS Gateway (API bên thứ 3) không chỉ là code, mà còn phải chờ nhà mạng duyệt hồ sơ đăng ký Brandname, test Sandbox rất mất thời gian. Quỹ thời gian 5 tuần là quá rủi ro.</t>
+  </si>
+  <si>
+    <t>Áp dụng tư duy quản lý rủi ro dự án phần mềm và kinh nghiệm làm việc với các hệ thống tích hợp ngoại vi (Third-party Integration).</t>
+  </si>
+  <si>
+    <t>Tôi đã phản bác lại AI, tự quyết định hạ cấp tính năng R03 xuống "Won't Have" (Không làm trong phiên bản này) và thay bằng giải pháp backup là Lễ tân gọi điện thoại.</t>
+  </si>
+  <si>
+    <t>Trong phần phân loại MoSCoW (Bài 1), AI tự động đề xuất R07 (Tích hợp thanh toán VNPay, MoMo) là tính năng "Must Have" vì cho rằng app y tế hiện đại nào cũng phải có thanh toán online.</t>
+  </si>
+  <si>
+    <t>Trong ngữ cảnh dự án chỉ có 8 tuần và 3 dev, mục tiêu cốt lõi (Core value) là giúp bệnh nhân lấy số thứ tự từ xa. Việc tích hợp cổng thanh toán đòi hỏi test bảo mật cực kỳ phức tạp. Nếu hệ thống thanh toán lỗi, bệnh nhân không đặt được lịch, phá vỡ luồng chính. Bệnh nhân hoàn toàn có thể trả tiền mặt tại quầy.</t>
+  </si>
+  <si>
+    <t>Đối chiếu với ràng buộc của đề bài (8 tuần, 3 dev) và định nghĩa "Must Have" (Không có tính năng này thì hệ thống có đáp ứng được mục đích chính không?).</t>
+  </si>
+  <si>
+    <t>Tôi đã bác bỏ AI, tự điều chỉnh R07 xuống "Could Have" (Có thì tốt) và giải thích rõ ưu tiên nguồn lực dev cho chức năng định danh và đặt lịch cơ bản.</t>
+  </si>
+  <si>
+    <t>Khi phân tích tình huống TH5 (Test Pass nhưng Giám đốc từ chối), AI kết luận rằng lỗi này thuộc về Tester (Verification) do chưa test kỹ trường hợp bệnh nhân không có thẻ BHYT.</t>
+  </si>
+  <si>
+    <t>Việc hệ thống bắt buộc nhập BHYT đã được ghi rõ trong tài liệu yêu cầu (SRS) ban đầu và Tester chỉ làm đúng chức trách là test theo SRS. Lỗi gốc rễ (Root cause) ở đây nằm ở khâu Validation (Lấy yêu cầu sai thực tế ngay từ đầu của BA), không phải lỗi Verification của Tester.</t>
+  </si>
+  <si>
+    <t>Áp dụng định nghĩa trong slide Chương 17: "Verification: Are we building the product right?" (Đúng tài liệu) vs "Validation: Are we building the right product?" (Đúng nhu cầu).</t>
+  </si>
+  <si>
+    <t>Tôi đã tự viết lại hoàn toàn phần lập luận phân tích TH5, khẳng định rõ đây là sự thất bại của quy trình Validation và đề xuất BA phải làm Mockup/Prototype từ sớm.</t>
+  </si>
+  <si>
+    <t>Khi sinh Acceptance Criteria (Bài 3), AI dùng các mô tả ở mệnh đề Then: "Hệ thống hoạt động tốt, tải dữ liệu nhanh chóng và cập nhật danh sách bác sĩ".</t>
+  </si>
+  <si>
+    <t>Nguyên tắc tối thượng của Acceptance Criteria là phải "Testable" (Có thể đo lường và kiểm chứng được bằng dữ liệu). Các cụm từ như "hoạt động tốt", "nhanh chóng" là mơ hồ (Ambiguous) và Tester không thể dựa vào đó để Pass/Fail một test case.</t>
+  </si>
+  <si>
+    <t>Kiểm tra đối chiếu với tiêu chuẩn viết yêu cầu tốt (Characteristics of a Good Requirement) và cấu trúc Given-When-Then chuẩn.</t>
+  </si>
+  <si>
+    <t>Tôi đã loại bỏ các từ ngữ mơ hồ của AI, thay bằng các tiêu chí có thể đo lường (Ví dụ: "Hệ thống hiển thị popup thành công, trừ đi 1 slot chỗ trống trong database, trả về mã phiếu khám định dạng #PKxxx").</t>
+  </si>
+  <si>
+    <t>Decomposition / Prioritization</t>
+  </si>
+  <si>
+    <t>Xác định phân loại ưu tiên (MoSCoW) cho 10 yêu cầu của hệ thống đặt lịch khám, đặc biệt trong tình huống deadline rút ngắn từ 8 tuần xuống 5 tuần.</t>
+  </si>
+  <si>
+    <t>"Phân loại MoSCoW cho 10 requirement sau của phòng khám. Nếu deadline còn 5 tuần thì nên cắt giảm tính năng nào?"</t>
+  </si>
+  <si>
+    <t>AI phân loại đúng các Must Have, nhưng đề xuất giữ lại tính năng "Hệ thống tự động gửi SMS" (R03) và cắt giảm "Báo cáo doanh thu" (R05) vì cho rằng nhắn tin cho bệnh nhân là quan trọng nhất.</t>
+  </si>
+  <si>
+    <t>Khuyến nghị của AI bỏ qua đánh giá rủi ro kỹ thuật (Technical Risk). Việc tích hợp SMS Gateway tốn nhiều thời gian đăng ký và kiểm duyệt với bên thứ 3. Tôi đã dùng "Human Delta" để quyết định hạ cấp R03 xuống "Won't Have", ưu tiên giữ nguồn lực dev cho tính năng đặt lịch cốt lõi và thay SMS bằng việc Lễ tân gọi điện thủ công. Quyết định này thực tế và khả thi hơn cho mốc thời gian 5 tuần.</t>
+  </si>
+  <si>
+    <t>Phần 1c — Điều chỉnh khi deadline bị rút ngắn (Bài tập 1)</t>
+  </si>
+  <si>
+    <t>Concept Mapping / Root Cause Analysis</t>
+  </si>
+  <si>
+    <t>Logic/Process Design / Use Case Specification</t>
+  </si>
+  <si>
+    <t>Cần phân tích nguyên nhân gốc rễ của tình huống TH5 (Test automated chạy PASS 100% nhưng Giám đốc từ chối dự án do sai quy trình nghiệp vụ).</t>
+  </si>
+  <si>
+    <t>Viết các tiêu chí nghiệm thu (Acceptance Criteria) cho chức năng "Đặt lịch khám trực tuyến" theo định dạng Given-When-Then đảm bảo testable (có thể kiểm thử).</t>
+  </si>
+  <si>
+    <t>"Phân tích TH5: Tại sao tester chạy pass 200 test case tự động nhưng dự án vẫn bị từ chối? Đây là lỗi của khâu nào?"</t>
+  </si>
+  <si>
+    <t>"Viết 4 Acceptance Criteria cho user story bệnh nhân đặt lịch khám trực tuyến bằng định dạng Given-When-Then."</t>
+  </si>
+  <si>
+    <t>AI phân tích chung chung và cho rằng lỗi thuộc về Tester đã không tạo đủ test case cho luồng bệnh nhân không có thẻ BHYT, đề xuất QA nên test kỹ hơn.</t>
+  </si>
+  <si>
+    <t>AI cung cấp các AC cơ bản theo happy-path. Tuy nhiên, ở mệnh đề Then, AI dùng các từ ngữ định tính: "Hệ thống tải danh sách nhanh chóng", "Giao diện hiển thị thành công".</t>
+  </si>
+  <si>
+    <t>AI bị nhầm lẫn ranh giới giữa Verification (Làm đúng tài liệu) và Validation (Làm đúng nhu cầu). Việc test PASS chứng tỏ Tester đã làm chuẩn Verification. Tôi đã phản bác logic của AI, phân tích lại rằng lỗi nằm ở BA ngay từ đầu khi viết SRS đi ngược lại luồng nghiệp vụ thực tế (Validation Failed). Tôi bổ sung thêm giải pháp phòng ngừa là làm Prototype và UAT thay vì chỉ rà soát test case.</t>
+  </si>
+  <si>
+    <t>AI vi phạm tiêu chuẩn "Measurability" (tính đo lường) của Requirement. Một QA không thể dựa vào chữ "nhanh chóng" để đánh giá Pass/Fail. Tôi đã loại bỏ hoàn toàn các từ mơ hồ do AI tạo ra, thay bằng thông số kỹ thuật rõ ràng: "Trừ đi 1 slot chỗ trống trong cơ sở dữ liệu", "Hiển thị popup chứa mã phiếu khám định dạng #PKxxx". Đồng thời, tôi tự thiết kế thêm 1 AC về "Race Condition" (2 người đặt cùng lúc) mà AI đã bỏ sót.</t>
+  </si>
+  <si>
+    <t>Phần 2b — Phân tích sâu tình huống TH5 (Bài tập 2)</t>
+  </si>
+  <si>
+    <t>Phần 3a &amp; 3b — Viết Acceptance Criteria (Bài tập 3)</t>
   </si>
 </sst>
 </file>
@@ -899,7 +1019,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -939,21 +1059,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1268,7 +1391,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="20"/>
@@ -1490,7 +1613,7 @@
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="20.6328125" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="29.1796875" customWidth="1"/>
+    <col min="4" max="4" width="31" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="32.6328125" customWidth="1"/>
     <col min="6" max="6" width="35" customWidth="1"/>
     <col min="7" max="7" width="84.6328125" customWidth="1"/>
@@ -1498,7 +1621,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="22" t="s">
         <v>37</v>
       </c>
       <c r="B1" s="20"/>
@@ -1510,7 +1633,7 @@
       <c r="H1" s="20"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="23" t="s">
         <v>38</v>
       </c>
       <c r="B2" s="20"/>
@@ -1910,34 +2033,82 @@
       </c>
     </row>
     <row r="18" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
+      <c r="A18" s="7">
+        <v>15</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="19" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
+      <c r="A19" s="7">
+        <v>16</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="20" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
+      <c r="A20" s="7">
+        <v>17</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="21" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="7"/>
@@ -1978,11 +2149,11 @@
     <col min="3" max="3" width="53.453125" customWidth="1"/>
     <col min="4" max="4" width="84.453125" customWidth="1"/>
     <col min="5" max="5" width="38.36328125" customWidth="1"/>
-    <col min="6" max="6" width="66" customWidth="1"/>
+    <col min="6" max="6" width="75.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="21" t="s">
         <v>50</v>
       </c>
       <c r="B1" s="20"/>
@@ -1992,7 +2163,7 @@
       <c r="F1" s="20"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="19" t="s">
         <v>51</v>
       </c>
       <c r="B2" s="20"/>
@@ -2242,44 +2413,104 @@
       </c>
     </row>
     <row r="15" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
+      <c r="A15" s="7">
+        <v>12</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="16" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
+      <c r="A16" s="7">
+        <v>13</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="17" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
+      <c r="A17" s="7">
+        <v>14</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="F17" s="25" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="18" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
+      <c r="A18" s="7">
+        <v>15</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="19" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
+      <c r="A19" s="7">
+        <v>16</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row r="20" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="7"/>
@@ -2389,7 +2620,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="22" t="s">
         <v>77</v>
       </c>
       <c r="B1" s="20"/>

--- a/AI_AuditLog_DoanNhat.xlsx
+++ b/AI_AuditLog_DoanNhat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Semester 5\SWR302\ai-audit-log-DoanNhat219\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA95F311-9E26-4C16-B3C9-338F938F9FA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0ADBFF0-479A-4A34-AFB4-87D1B942048D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="16090" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11170" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -1059,24 +1059,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1394,11 +1394,11 @@
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="3" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
@@ -1624,25 +1624,25 @@
       <c r="A1" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
     </row>
     <row r="3" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
@@ -2153,24 +2153,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
     </row>
     <row r="3" spans="1:6" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
@@ -2468,7 +2468,7 @@
       <c r="E17" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="F17" s="25" t="s">
+      <c r="F17" s="19" t="s">
         <v>255</v>
       </c>
     </row>
@@ -2623,17 +2623,17 @@
       <c r="A1" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
     </row>
     <row r="4" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">

--- a/AI_AuditLog_DoanNhat.xlsx
+++ b/AI_AuditLog_DoanNhat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Semester 5\SWR302\ai-audit-log-DoanNhat219\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0ADBFF0-479A-4A34-AFB4-87D1B942048D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8E2D6E3-3B9C-4849-9E66-37C68D6D76F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11170" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="16090" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="314">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -880,6 +880,102 @@
   </si>
   <si>
     <t>Phần 3a &amp; 3b — Viết Acceptance Criteria (Bài tập 3)</t>
+  </si>
+  <si>
+    <t>Elicitation / Games People Play</t>
+  </si>
+  <si>
+    <t>Validation Concept</t>
+  </si>
+  <si>
+    <t>Test Case Design</t>
+  </si>
+  <si>
+    <t>Xây dựng Test Case chuẩn xác cho Acceptance Criteria: Xử lý ngoại lệ khi "Bỏ trống trường dữ liệu bắt buộc" trong quy trình đặt lịch khám.</t>
+  </si>
+  <si>
+    <t>Xác định hành động BA cho bác sĩ dùng thử prototype và hỏi ý kiến xem có hợp quy trình không (Tình huống TH2) là Verification hay Validation.</t>
+  </si>
+  <si>
+    <t>Xây dựng bộ câu hỏi phản biện (Games People Play) để kiểm tra tính cần thiết của yêu cầu "Bác sĩ xem lịch khám trong ngày trên app mobile" (R02 - Should Have).</t>
+  </si>
+  <si>
+    <t>"Đóng vai BA, hãy viết 3 câu hỏi theo kỹ thuật 'Games People Play' để hỏi khách hàng xem tính năng App Mobile cho bác sĩ có thực sự cần thiết trong giai đoạn 1 không."</t>
+  </si>
+  <si>
+    <t>AI đưa ra các câu hỏi thiên về thu thập UI/UX hoặc hỏi trực tiếp: "Bác sĩ có thích dùng app mobile không?", "Giao diện app nên có những nút bấm nào?".</t>
+  </si>
+  <si>
+    <t>"Hành động cho khách hàng dùng prototype rồi hỏi xem có phù hợp quy trình không (TH2) là Verification hay Validation? Hãy giải thích lý do."</t>
+  </si>
+  <si>
+    <t>AI trả lời đúng đáp án là Validation, nhưng phần giải thích lại lan man về việc tester phải rà soát lỗi giao diện của prototype và viết test case cho nó như thế nào.</t>
+  </si>
+  <si>
+    <t>"Viết 1 test case chi tiết cho trường hợp bệnh nhân để trống ô 'Triệu chứng hiện tại' khi bấm nút đặt lịch khám."</t>
+  </si>
+  <si>
+    <t>AI tạo form test case có đủ các bước (Steps), nhưng ở phần "Dữ liệu thử" (Test Data) lại ghi chung chung là "Nhập thông tin sai" và "Kết quả mong đợi" chỉ ghi ngắn gọn là "Hệ thống báo lỗi".</t>
+  </si>
+  <si>
+    <t>Các câu hỏi do AI tạo ra mang tính chất thu thập yêu cầu thiết kế (Design requirement) chứ không thách thức giá trị cốt lõi (Challenge the value) theo đúng tinh thần "Games People Play" học trên lớp. Tôi đã tự điều chỉnh lại câu hỏi, xoáy sâu vào các Workarounds (giải pháp thay thế) và ROI: "Nếu dùng Zalo gửi lịch khám thay vì xây app thì sao?", "Dời tính năng này sang Phase 2 có ảnh hưởng gì không?". Việc này giúp BA nắm được quyền chủ động.</t>
+  </si>
+  <si>
+    <t>Phần 1b — Đặt câu hỏi kiểu "Games People Play" (Bài tập 1)</t>
+  </si>
+  <si>
+    <t>Lập luận của AI bị lạc đề và mang hơi hướng của Verification (kiểm thử phần mềm). Tôi đã chủ động lược bỏ các ý thừa của AI, tự viết lại phần giải thích đi thẳng vào bản chất: Validation là "Are we building the right product?" - Xác nhận trực tiếp với end-user (Bác sĩ) xem sản phẩm có giải quyết đúng vấn đề thực tiễn không, tách biệt hoàn toàn với việc rà soát lỗi code.</t>
+  </si>
+  <si>
+    <t>Phần 2a — Phân tích tình huống TH2 (Bài tập 2)</t>
+  </si>
+  <si>
+    <t>Test case của AI thiếu tính đặc tả dữ liệu (Data Specification). Một QA không thể test nếu chỉ đọc "Hệ thống báo lỗi". Tôi đã bổ sung sự chặt chẽ (Human Delta) bằng cách quy định rõ Pre-condition (Tài khoản phải hợp lệ), chốt Test Data (Ô Triệu chứng = [Null/Rỗng]) và mô tả chi tiết UI ở Expected Result (Viền đỏ ô nhập liệu, xuất hiện dòng text đỏ "Vui lòng nhập triệu chứng"). Điều này đảm bảo test case có thể thực thi ngay trong dự án thật.</t>
+  </si>
+  <si>
+    <t>Phần 3c — Thiết kế test case (Bài tập 3)</t>
+  </si>
+  <si>
+    <t>Scope Creep / Context Ignorance</t>
+  </si>
+  <si>
+    <t>Khi phân loại MoSCoW, AI gợi ý đánh giá yêu cầu R08 ("Bác sĩ ghi chú điện tử thay vì hồ sơ giấy") là "Must Have", với lý do "các phòng khám hiện đại bắt buộc phải chuyển đổi số và bỏ sổ khám bệnh giấy".</t>
+  </si>
+  <si>
+    <t>Concept Confusion / Logic Error</t>
+  </si>
+  <si>
+    <t>Khi phân tích tình huống TH3 ("Team review lại SRS để đảm bảo có test case"), AI cho rằng đây là "Validation" vì nó nhắc đến từ khóa "Acceptance test" (Kiểm thử nghiệm thu).</t>
+  </si>
+  <si>
+    <t>Khi viết Acceptance Criteria cho việc đăng ký bằng SĐT (R01), AI chỉ đưa ra luồng: Nhập SĐT -&gt; Nhấn gửi -&gt; Nhận OTP. AI hoàn toàn bỏ qua việc kiểm tra định dạng dữ liệu đầu vào.</t>
+  </si>
+  <si>
+    <t>Đề bài quy định rõ mục tiêu cốt lõi của V1 là "ứng dụng đặt lịch khám" với tài nguyên cực hạn hẹp (8 tuần, 3 dev). Việc xây dựng hệ thống Bệnh án điện tử (EMR - Electronic Medical Records) là một module khổng lồ, phức tạp và hoàn toàn nằm ngoài phạm vi cốt lõi (Out of scope) của giai đoạn 1.</t>
+  </si>
+  <si>
+    <t>Rà soát chéo tài liệu (SRS vs Test Cases) để đảm bảo tính truy vết (Traceability) là hoạt động kiểm tra tĩnh nội bộ. Nó đối chiếu giữa các tài liệu với nhau xem có khớp không, chứ không lấy ý kiến khách hàng. Do đó, bản chất của nó là Verification (Làm đúng quy trình/tài liệu).</t>
+  </si>
+  <si>
+    <t>Hệ thống thực tế nếu không có Validation ở frontend/backend, người dùng có thể nhập chữ cái hoặc SĐT chỉ có 5 số, dẫn đến việc API gửi SMS bị lỗi crash server hoặc tốn tiền vô ích.</t>
+  </si>
+  <si>
+    <t>Đối chiếu gợi ý của AI với phần "Ngữ cảnh" của đề bài (Tài nguyên và Mục tiêu dự án) và nguyên lý xác định ranh giới hệ thống (System Boundaries) trong môn SWR302.</t>
+  </si>
+  <si>
+    <t>Kiểm tra chéo với định nghĩa "Verification vs Validation" trong slide Chương 17: Validation bắt buộc phải trả lời câu hỏi "Sản phẩm có đúng nhu cầu thực tế của user không?".</t>
+  </si>
+  <si>
+    <t>Áp dụng nguyên tắc kiểm thử hộp đen (Black-box testing) đối với các trường nhập liệu (Input Fields) bắt buộc.</t>
+  </si>
+  <si>
+    <t>Tôi đã bác bỏ lập luận của AI, giáng cấp R08 xuống "Won't Have" và viết lại lý do: Cần dồn 100% nguồn lực dev cho luồng đặt lịch, tính năng ghi chú y khoa sẽ làm vỡ tiến độ dự án.</t>
+  </si>
+  <si>
+    <t>Tôi đã đổi phân loại thành "Verification", đồng thời viết lại phần giải thích để làm rõ: "Đây là quá trình review tài liệu nội bộ, đảm bảo tính đầy đủ (Traceability) trước khi code, không liên quan đến việc đánh giá giá trị thực tế".</t>
+  </si>
+  <si>
+    <t>Tôi đã tự TẠO THÊM một Acceptance Criteria về Validation Error: "Given user ở màn hình nhập SĐT / When user nhập số sai định dạng (ví dụ thiếu số, chứa chữ cái) / Then hệ thống báo lỗi định dạng ngay lập tức và không gọi API gửi OTP".</t>
   </si>
 </sst>
 </file>
@@ -992,7 +1088,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1015,11 +1111,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1062,12 +1178,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1075,8 +1194,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1391,7 +1513,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="21"/>
@@ -1607,7 +1729,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1621,7 +1743,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="20" t="s">
         <v>37</v>
       </c>
       <c r="B1" s="21"/>
@@ -1633,7 +1755,7 @@
       <c r="H1" s="21"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="23" t="s">
         <v>38</v>
       </c>
       <c r="B2" s="21"/>
@@ -2111,24 +2233,82 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-    </row>
-    <row r="22" spans="1:8" ht="80" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
+      <c r="A21" s="7">
+        <v>18</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="94.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="7">
+        <v>19</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="126" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="26">
+        <v>20</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="C23" s="26" t="s">
+        <v>284</v>
+      </c>
+      <c r="D23" s="26" t="s">
+        <v>285</v>
+      </c>
+      <c r="E23" s="26" t="s">
+        <v>292</v>
+      </c>
+      <c r="F23" s="26" t="s">
+        <v>293</v>
+      </c>
+      <c r="G23" s="26" t="s">
+        <v>298</v>
+      </c>
+      <c r="H23" s="26" t="s">
+        <v>299</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2153,7 +2333,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>50</v>
       </c>
       <c r="B1" s="21"/>
@@ -2163,7 +2343,7 @@
       <c r="F1" s="21"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="24" t="s">
         <v>51</v>
       </c>
       <c r="B2" s="21"/>
@@ -2513,20 +2693,64 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
+      <c r="A20" s="7">
+        <v>17</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>311</v>
+      </c>
     </row>
     <row r="21" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
+      <c r="A21" s="7">
+        <v>18</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="26">
+        <v>19</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>304</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>307</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>310</v>
+      </c>
+      <c r="F22" s="27" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="27" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
@@ -2620,7 +2844,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="20" t="s">
         <v>77</v>
       </c>
       <c r="B1" s="21"/>
@@ -2628,7 +2852,7 @@
       <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="22" t="s">
         <v>78</v>
       </c>
       <c r="B2" s="21"/>

--- a/AI_AuditLog_DoanNhat.xlsx
+++ b/AI_AuditLog_DoanNhat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Semester 5\SWR302\ai-audit-log-DoanNhat219\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8E2D6E3-3B9C-4849-9E66-37C68D6D76F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{982F0037-B557-47F5-8A08-A21E150CDB47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="16090" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="16090" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="353">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -976,6 +976,123 @@
   </si>
   <si>
     <t>Tôi đã tự TẠO THÊM một Acceptance Criteria về Validation Error: "Given user ở màn hình nhập SĐT / When user nhập số sai định dạng (ví dụ thiếu số, chứa chữ cái) / Then hệ thống báo lỗi định dạng ngay lập tức và không gọi API gửi OTP".</t>
+  </si>
+  <si>
+    <t>Xác định các thực thể bên ngoài (Actors) và tương tác chính để vẽ Context Diagram cho hệ thống SnakeGuard.</t>
+  </si>
+  <si>
+    <t>Workflow Design</t>
+  </si>
+  <si>
+    <t>Kiểm tra độ chính xác và logic nghiệp vụ của bản nháp Use Case Diagram đã tự vẽ trên Visual Paradigm.</t>
+  </si>
+  <si>
+    <t>Xây dựng Conceptual ERD dựa trên Use Case và yêu cầu nghiệp vụ quản lý rắn và cứu hộ.</t>
+  </si>
+  <si>
+    <t>Đảm bảo các mô tả nghiệp vụ (Descriptions) cho các Actors, Use Cases và Entities sử dụng chính xác thuật ngữ tiếng Anh theo chuẩn form mẫu.</t>
+  </si>
+  <si>
+    <t>Cung cấp toàn bộ text đề thi PE SWR302_FA25_PE1 và yêu cầu AI thiết kế Context Diagram xuất ra file .drawio.</t>
+  </si>
+  <si>
+    <t>Gửi ảnh chụp màn hình bản nháp Use Case Diagram hệ thống SnakeGuard và hỏi: "Như này oke chưa bạn. Lưu ý chính xác nghiệp vụ."</t>
+  </si>
+  <si>
+    <t>Gợi ý của AI chính xác về mặt cấu trúc. Tuy nhiên, AI để mũi tên 2 chiều chung chung. Tôi nhận thức được quy định gắt gao của đề SWR302 về keyword, nên đã tự rà soát và bổ sung chi tiết các luồng dữ liệu (Data flows) trên mũi tên sao cho khớp 100% với đề (VD: Citizen gửi "Images/Videos, GPS", nhận "AI safety warnings") thay vì bê nguyên xi hình vẽ của AI.</t>
+  </si>
+  <si>
+    <t>AI đã giúp tôi phát hiện rủi ro chí mạng. Dựa trên góp ý đó, tôi đã quyết định XÓA Use Case "Register/Login" (vì đề chỉ ghi "Citizens log into...", gộp vào precondition). Đồng thời, tôi chủ động cấu trúc lại layout của các luồng &lt;&lt;include&gt;&gt; và &lt;&lt;extend&gt;&gt;, tách biệt rõ khu vực của Citizen và Admin để giảm thiểu các đường nối cắt chéo nhau, giúp sơ đồ mạch lạc và tối ưu hơn cho giám khảo chấm bài.</t>
+  </si>
+  <si>
+    <t>Context Diagram</t>
+  </si>
+  <si>
+    <t>Use Case Diagram hoàn thiện</t>
+  </si>
+  <si>
+    <t>Yêu cầu AI thiết kế Conceptual ERD dựa trên answer của câu 2 và 3, mô tả ngắn gọn các thực thể.</t>
+  </si>
+  <si>
+    <t>Yêu cầu AI viết các đoạn mô tả ngắn gọn (Briefly describe) bằng tiếng Anh để điền vào template bài thi.</t>
+  </si>
+  <si>
+    <t>AI đề xuất 6 thực thể chính (User, SnakeReport, SnakeSpecies, RescueTask, CommunityPost, DangerZone) và các mối quan hệ (1:N, N:1) cơ bản.</t>
+  </si>
+  <si>
+    <t>AI định hình cấu trúc thực thể rất tốt. Tuy nhiên, để thể hiện rõ sự hiểu biết về cơ sở dữ liệu, tôi đã tự suy luận và quyết định áp dụng cơ chế Kế thừa (Inheritance/Generalization) cho thực thể "User". Cụ thể, "User" là Super-type, còn Citizen, Expert, Rescue Team, Admin là các Sub-types, giúp tối ưu hóa việc quản lý tài khoản được nhắc đến trong Use Case của Admin thay vì thiết kế phẳng (flat design) như AI ban đầu.</t>
+  </si>
+  <si>
+    <t>Conceptual ERD</t>
+  </si>
+  <si>
+    <t>AI generate các đoạn văn tóm tắt chức năng của từng Actor, Use Case và Entity với câu từ mạch lạc, trơn tru.</t>
+  </si>
+  <si>
+    <t>AI viết tiếng Anh tốt, nhưng có xu hướng diễn đạt lại theo cách khác (paraphrase). Để đảm bảo an toàn tuyệt đối, tôi đã đối chiếu lại từng câu của AI với text gốc của đề bài, cắt bỏ những cụm từ "bay bổng" thừa thãi của AI và thay thế lại bằng chính xác keyword của đề (Ví dụ: Đảm bảo giữ nguyên cụm "identify seasonal or weather-related factors" cho Expert).</t>
+  </si>
+  <si>
+    <t>Document/Template bài làm phần Description.</t>
+  </si>
+  <si>
+    <t>Over-specification / Out-of-Scope (Làm lố/Vượt phạm vi)</t>
+  </si>
+  <si>
+    <t>Omission (Thiếu sót)</t>
+  </si>
+  <si>
+    <t>Logic Error / Structural Flaw (Lỗi cấu trúc logic)</t>
+  </si>
+  <si>
+    <t>Business Rule Violation (Sai quy tắc nghiệp vụ)</t>
+  </si>
+  <si>
+    <t>Khi vẽ Use Case Diagram, AI tự động tạo và thêm các Use Case "Register" và "Login" cho đối tượng Citizen vì cho rằng đây là tính năng cơ bản bắt buộc của mọi app.</t>
+  </si>
+  <si>
+    <t>Ở bản phác thảo Context Diagram ban đầu, AI chỉ vẽ các mũi tên 2 chiều (Bidirectional lines) nối giữa các Actors và System mà không dán nhãn (label) dữ liệu gì truyền trên đó.</t>
+  </si>
+  <si>
+    <t>Khi tạo Conceptual ERD, AI thiết lập một mối quan hệ (Relationship) trực tiếp nối thẳng từ thực thể Citizen sang RescueTeam.</t>
+  </si>
+  <si>
+    <t>AI gán quyền (Association) cho Actor "Rescue Team" được phép thực hiện Use Case "Verify Snake Report" (Xác minh loại rắn).</t>
+  </si>
+  <si>
+    <t>Đề bài có dòng cảnh báo đỏ gắt gao: "Any keywords not related to this electronic exam paper... get ZERO". Đề bài chỉ dùng cụm "Citizens log into the system" như một tiền điều kiện, không yêu cầu phân tích sâu thành Use Case riêng biệt lẻ tẻ.</t>
+  </si>
+  <si>
+    <t>Trong chuẩn thiết kế Context Diagram (môn SWR302), các luồng mũi tên phải mô tả rõ Data Flows (Dữ liệu vào/ra). Đề bài ghi rõ Rescue Team nhận "AI-detected data and actual visuals".</t>
+  </si>
+  <si>
+    <t>Đối chiếu từng Use Case (oval) AI xuất ra với các cụm động từ nghiệp vụ (business verbs) được mô tả trực tiếp trong văn bản đề thi.</t>
+  </si>
+  <si>
+    <t>Dựa trên kiến thức chuẩn về sơ đồ Context Diagram và so sánh với mô tả luồng tương tác chi tiết của từng Actor trong đề thi.</t>
+  </si>
+  <si>
+    <t>XÓA bỏ hoàn toàn các Use Case liên quan đến Account Registration/Login. Chỉ giữ lại các Use Case đúng keyword của đề như "Report Snake Sighting", "Track Rescue Status".</t>
+  </si>
+  <si>
+    <t>Tự bổ sung text chi tiết (Label) lên các đường mũi tên. Cụ thể: Mũi tên từ System -&gt; Rescue Team ghi rõ là "AI-detected data, visuals, notifications".</t>
+  </si>
+  <si>
+    <t>Dựa theo logic hệ thống nền tảng (Platform), người dân báo cáo cho Hệ thống, Hệ thống điều phối Cứu hộ. Hai đối tượng này không kết nối trực tiếp với nhau mà qua các ticket/report trung gian.</t>
+  </si>
+  <si>
+    <t>Đọc kỹ đoạn 3 của đề bài: "In cases where identification is difficult... experts are notified by the system to verify the report." Nghiệp vụ Verify hoàn toàn thuộc về nhóm Chuyên gia (Experts)</t>
+  </si>
+  <si>
+    <t>Áp dụng tư duy phân tích cơ sở dữ liệu. Nhận thấy nếu nối trực tiếp 2 Actors sẽ làm vô hiệu hóa vai trò quản lý trung tâm của SnakeGuard System.</t>
+  </si>
+  <si>
+    <t>Rà soát lại từng chủ ngữ (Subject) đi liền với hành động nghiệp vụ (Action/Verb) trong câu tiếng Anh của đề bài (Ma trận phân quyền).</t>
+  </si>
+  <si>
+    <t>Bác bỏ liên kết trực tiếp. Thiết kế lại ERD theo luồng: Citizen (1) - (N) SnakeReport, và RescueTeam (1) - (N) RescueTask. Hệ thống kết nối Report và Task.</t>
+  </si>
+  <si>
+    <t>Xóa đường nối (Association line) giữa "Rescue Team" và "Verify Snake Report". Đảm bảo chỉ có Actor "Expert" mới được nối với Use Case này.</t>
   </si>
 </sst>
 </file>
@@ -1135,7 +1252,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1178,20 +1295,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1513,14 +1636,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
     </row>
     <row r="3" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
@@ -1729,7 +1852,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1743,28 +1866,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
@@ -2285,29 +2408,133 @@
       </c>
     </row>
     <row r="23" spans="1:8" ht="126" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="26">
+      <c r="A23" s="20">
         <v>20</v>
       </c>
-      <c r="B23" s="26" t="s">
+      <c r="B23" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="C23" s="26" t="s">
+      <c r="C23" s="20" t="s">
         <v>284</v>
       </c>
-      <c r="D23" s="26" t="s">
+      <c r="D23" s="20" t="s">
         <v>285</v>
       </c>
-      <c r="E23" s="26" t="s">
+      <c r="E23" s="20" t="s">
         <v>292</v>
       </c>
-      <c r="F23" s="26" t="s">
+      <c r="F23" s="20" t="s">
         <v>293</v>
       </c>
-      <c r="G23" s="26" t="s">
+      <c r="G23" s="20" t="s">
         <v>298</v>
       </c>
-      <c r="H23" s="26" t="s">
+      <c r="H23" s="20" t="s">
         <v>299</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="111.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="20">
+        <v>21</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>319</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>321</v>
+      </c>
+      <c r="H24" s="20" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="100.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="20">
+        <v>22</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>315</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>316</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>316</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>320</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>322</v>
+      </c>
+      <c r="H25" s="20" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="63" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="20">
+        <v>23</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>317</v>
+      </c>
+      <c r="E26" s="28" t="s">
+        <v>325</v>
+      </c>
+      <c r="F26" s="28" t="s">
+        <v>327</v>
+      </c>
+      <c r="G26" s="28" t="s">
+        <v>328</v>
+      </c>
+      <c r="H26" s="28" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="93" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="20">
+        <v>24</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>318</v>
+      </c>
+      <c r="E27" s="28" t="s">
+        <v>326</v>
+      </c>
+      <c r="F27" s="28" t="s">
+        <v>330</v>
+      </c>
+      <c r="G27" s="28" t="s">
+        <v>331</v>
+      </c>
+      <c r="H27" s="28" t="s">
+        <v>332</v>
       </c>
     </row>
   </sheetData>
@@ -2333,24 +2560,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
     </row>
     <row r="3" spans="1:6" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
@@ -2733,23 +2960,103 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="26">
+      <c r="A22" s="20">
         <v>19</v>
       </c>
-      <c r="B22" s="26" t="s">
+      <c r="B22" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="C22" s="20" t="s">
         <v>304</v>
       </c>
-      <c r="D22" s="26" t="s">
+      <c r="D22" s="20" t="s">
         <v>307</v>
       </c>
-      <c r="E22" s="26" t="s">
+      <c r="E22" s="20" t="s">
         <v>310</v>
       </c>
-      <c r="F22" s="27" t="s">
+      <c r="F22" s="21" t="s">
         <v>313</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="28">
+        <v>20</v>
+      </c>
+      <c r="B23" s="28" t="s">
+        <v>333</v>
+      </c>
+      <c r="C23" s="28" t="s">
+        <v>337</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="E23" s="28" t="s">
+        <v>343</v>
+      </c>
+      <c r="F23" s="29" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="28">
+        <v>21</v>
+      </c>
+      <c r="B24" s="28" t="s">
+        <v>334</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>338</v>
+      </c>
+      <c r="D24" s="28" t="s">
+        <v>342</v>
+      </c>
+      <c r="E24" s="28" t="s">
+        <v>344</v>
+      </c>
+      <c r="F24" s="29" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="90.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="28">
+        <v>22</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>335</v>
+      </c>
+      <c r="C25" s="28" t="s">
+        <v>339</v>
+      </c>
+      <c r="D25" s="28" t="s">
+        <v>347</v>
+      </c>
+      <c r="E25" s="28" t="s">
+        <v>349</v>
+      </c>
+      <c r="F25" s="29" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="80" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="28">
+        <v>23</v>
+      </c>
+      <c r="B26" s="29" t="s">
+        <v>336</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="D26" s="28" t="s">
+        <v>348</v>
+      </c>
+      <c r="E26" s="28" t="s">
+        <v>350</v>
+      </c>
+      <c r="F26" s="29" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -2844,20 +3151,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
     </row>
     <row r="4" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">

--- a/AI_AuditLog_DoanNhat.xlsx
+++ b/AI_AuditLog_DoanNhat.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Semester 5\SWR302\ai-audit-log-DoanNhat219\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{982F0037-B557-47F5-8A08-A21E150CDB47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E9A72EC-07D9-4ADF-AD25-155459C0C023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="16090" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="16090" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="416">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -1093,6 +1093,207 @@
   </si>
   <si>
     <t>Xóa đường nối (Association line) giữa "Rescue Team" và "Verify Snake Report". Đảm bảo chỉ có Actor "Expert" mới được nối với Use Case này.</t>
+  </si>
+  <si>
+    <t>Technical Feasibility Ignorance</t>
+  </si>
+  <si>
+    <t>Khi phân loại MoSCoW, AI xếp R10 ("Hiển thị thời gian chờ dự kiến theo thời gian thực") vào nhóm "Could Have" vì cho rằng tính năng này chỉ là những phép tính cộng trừ thời gian đơn giản để tăng trải nghiệm người dùng.</t>
+  </si>
+  <si>
+    <t>Syntax Violation</t>
+  </si>
+  <si>
+    <t>Khi sinh Acceptance Criteria (AC) cho chức năng đặt lịch, AI viết nhầm lẫn vai trò của các mệnh đề: "Given: Bệnh nhân bấm nút Xác nhận" và "When: Hệ thống đang ở màn hình điền thông tin".</t>
+  </si>
+  <si>
+    <t>Để hệ thống hiển thị thời gian chờ "Real-time" chính xác, phần mềm phải kết nối liên tục (WebSockets) với hệ thống gọi số vật lý tại cả 3 cơ sở của phòng khám. Việc này đòi hỏi kỹ thuật phức tạp, hoàn toàn bất khả thi đối với team 3 developer trong quỹ thời gian 8 tuần.</t>
+  </si>
+  <si>
+    <t>Định dạng Given-When-Then có quy tắc nghiêm ngặt: 'Given' dùng để mô tả điều kiện tiên quyết (Trạng thái ban đầu), còn 'When' dùng để mô tả hành động kích hoạt (Trigger). Việc AI đảo ngược hai mệnh đề này khiến test case trở nên vô nghĩa về mặt logic.</t>
+  </si>
+  <si>
+    <t>Áp dụng tư duy đánh giá tính khả thi kỹ thuật (Technical Feasibility) và đối chiếu với ràng buộc nguồn lực dự án (3 Devs, 8 weeks).</t>
+  </si>
+  <si>
+    <t>Tôi đã hạ cấp R10 xuống thẳng nhóm "Won't Have" (Không làm trong phiên bản này) và đưa ra lập luận chặt chẽ về việc thiếu hụt nguồn lực và rủi ro công nghệ.</t>
+  </si>
+  <si>
+    <t>Đối chiếu với quy tắc viết Behavior-Driven Development (BDD) / Given-When-Then chuẩn trong tài liệu SWR302 (Chương 17).</t>
+  </si>
+  <si>
+    <t>Tôi đã tự cấu trúc lại AC chuẩn xác: Given (Bệnh nhân đang ở màn hình đặt lịch và đã điền đủ thông tin) -&gt; When (Bệnh nhân click nút Xác nhận) -&gt; Then (Lưu vào database và báo thành công).</t>
+  </si>
+  <si>
+    <t>Concept Overlap</t>
+  </si>
+  <si>
+    <t>Ở tình huống TH4 (PM rà soát Business Requirements và Software Requirements), AI nhận định đây là "Cả hai" (Verification và Validation) với lý do PM đang đọc yêu cầu kinh doanh của khách hàng nên tính là Validation.</t>
+  </si>
+  <si>
+    <t>Hành động PM đọc, đối chiếu và so sánh giữa hai bản tài liệu (Static Review / Traceability) để tìm chỗ dịch sai hoàn toàn là Verification. Khâu này chưa hề có phần mềm chạy thử nghiệm hay có mặt người dùng cuối (Bác sĩ/Bệnh nhân) để xác nhận, nên không thể gọi là Validation.</t>
+  </si>
+  <si>
+    <t>Kiểm tra lại định nghĩa của Validation: "Are we building the right product?" - Đòi hỏi việc chứng minh sản phẩm giải quyết đúng nhu cầu trong môi trường thực tiễn, không phải chỉ là review tài liệu.</t>
+  </si>
+  <si>
+    <t>Tôi đã sửa lại đáp án thành "Chỉ Verification", đồng thời giải thích rõ đây là hoạt động kiểm tra tĩnh (Static Testing/Review nội bộ) đảm bảo tài liệu được chuyển đổi chính xác.</t>
+  </si>
+  <si>
+    <t>AI liệt kê thiếu các bước, bỏ sót rào cản dữ liệu quan trọng.</t>
+  </si>
+  <si>
+    <t>AI vi phạm các nguyên tắc thiết kế, sai cấu trúc tiêu chuẩn.</t>
+  </si>
+  <si>
+    <t>AI tự suy diễn, mặc định các hành động kỹ thuật gây rủi ro cao.</t>
+  </si>
+  <si>
+    <t>Quên mất bước kiểm tra tính hợp lệ của dữ liệu đầu vào (Validation Input) khi người dùng nhập số điện thoại.</t>
+  </si>
+  <si>
+    <t>Viết Acceptance Criteria dùng từ ngữ mơ hồ ("hoạt động tốt") hoặc viết ngược mệnh đề Given và When.</t>
+  </si>
+  <si>
+    <t>Đề xuất hành động xóa trực tiếp (Hard Delete) dữ liệu lịch khám thay vì vô hiệu hóa (Soft Delete/Cancel).</t>
+  </si>
+  <si>
+    <t>Oversimplification / Logic Omission</t>
+  </si>
+  <si>
+    <t>AI đơn giản hóa vấn đề quá mức, dẫn đến bỏ sót các nhánh logic nghiệp vụ (Alternative flows).</t>
+  </si>
+  <si>
+    <t>AI đề xuất phương án đi ngược lại quy tắc kinh doanh hoặc phá hỏng tính toàn vẹn của cơ sở dữ liệu.</t>
+  </si>
+  <si>
+    <t>Đề xuất luồng thanh toán (Payment) luôn thành công, bỏ qua việc xử lý khi thẻ bị từ chối hoặc rớt mạng.</t>
+  </si>
+  <si>
+    <t>Đề xuất xóa vĩnh viễn (Hard Delete) hồ sơ bệnh nhân cũ thay vì vô hiệu hóa, làm mất lịch sử khám bệnh.</t>
+  </si>
+  <si>
+    <t>AI bỏ quên các điều kiện ràng buộc quan trọng, dễ tạo ra lỗ hổng bảo mật cho hệ thống.</t>
+  </si>
+  <si>
+    <t>Thiết kế luồng nhập mã OTP nhưng không yêu cầu giới hạn thời gian (Timeout) hoặc số lần nhập sai tối đa.</t>
+  </si>
+  <si>
+    <t>AI tự động vẽ thêm các tính năng quá chi tiết, phức tạp hoặc không thuộc phạm vi cam kết của dự án.</t>
+  </si>
+  <si>
+    <t>AI mở rộng phạm vi yêu cầu vô tội vạ, hoàn toàn ngó lơ bối cảnh và nguồn lực hạn hẹp của dự án.</t>
+  </si>
+  <si>
+    <t>AI vi phạm các nguyên tắc luận lý cơ bản hoặc thiết kế sai cấu trúc tài liệu chuẩn.</t>
+  </si>
+  <si>
+    <t>Gợi ý xây dựng hệ thống Bệnh án điện tử (EMR) khổng lồ trong khi dự án chỉ có 3 Dev và deadline 8 tuần.</t>
+  </si>
+  <si>
+    <t>Viết Acceptance Criteria nhưng lại đặt hành động (Action) vào mệnh đề "Given" thay vì "When".</t>
+  </si>
+  <si>
+    <t>Yêu cầu bệnh nhân phải quét khuôn mặt (FaceID) hoặc xác thực sinh trắc học mới được phép đặt lịch khám.</t>
+  </si>
+  <si>
+    <t>AI đề xuất các giải pháp không khả thi về mặt kỹ thuật so với hạ tầng hoặc thời gian cho phép.</t>
+  </si>
+  <si>
+    <t>AI tự đưa ra các giả định mang tính rủi ro cao mà không có căn cứ từ tài liệu Elicitation (thu thập yêu cầu).</t>
+  </si>
+  <si>
+    <t>AI nhầm lẫn giữa các khái niệm lý thuyết nền tảng của kỹ nghệ phần mềm.</t>
+  </si>
+  <si>
+    <t>AI viết sai cú pháp hoặc định dạng bắt buộc của một chuẩn tài liệu.</t>
+  </si>
+  <si>
+    <t>AI bỏ sót hoàn toàn một yếu tố cấu thành bắt buộc trong mô hình hoặc tài liệu.</t>
+  </si>
+  <si>
+    <t>Đề xuất làm hệ thống cập nhật số thứ tự thời gian thực (Real-time WebSockets) trong khi server không hỗ trợ.</t>
+  </si>
+  <si>
+    <t>Mặc định rằng mọi bệnh nhân đều có thẻ BHYT và bắt buộc nhập mã BHYT để đặt lịch.</t>
+  </si>
+  <si>
+    <t>Đánh giá sai bản chất của việc rà soát tài liệu (Verification) thành nghiệm thu tính năng thực tế (Validation).</t>
+  </si>
+  <si>
+    <t>Viết User Story không đúng cấu trúc "As a... I want to... So that...".</t>
+  </si>
+  <si>
+    <t>Quên không định nghĩa luồng xử lý đồng thời (Race condition) khi có 2 bệnh nhân cùng đặt 1 chỗ trống.</t>
+  </si>
+  <si>
+    <t>Abstraction / Prioritization</t>
+  </si>
+  <si>
+    <t>Business Rules Specification</t>
+  </si>
+  <si>
+    <t>Đánh giá và so sánh mức độ ưu tiên giữa R05 (Giám đốc xem báo cáo) và R06 (Đặt lịch tại 3 cơ sở) trong bối cảnh quỹ thời gian dự án ngắn.</t>
+  </si>
+  <si>
+    <t>Cần viết Acceptance Criteria (AC) chặt chẽ cho thao tác chọn ngày/giờ khám của Bệnh nhân để đảm bảo tính toàn vẹn dữ liệu.</t>
+  </si>
+  <si>
+    <t>"Phân loại MoSCoW cho R05 và R06. Đứng ở góc độ quản lý phòng khám, tính năng nào nên được ưu tiên làm trước?"</t>
+  </si>
+  <si>
+    <t>"Hãy viết luồng Acceptance Criteria cho thao tác chọn ngày giờ khám của bệnh nhân."</t>
+  </si>
+  <si>
+    <t>AI gợi ý R05 là "Must Have" vì lãnh đạo luôn cần xem số liệu tài chính, và đánh giá R06 là "Could Have" để giảm tải việc thiết kế database đa cơ sở cho Developer.</t>
+  </si>
+  <si>
+    <t>AI đưa ra luồng rất đơn giản: Given user mở ứng dụng -&gt; When user chọn ngày giờ -&gt; Then hệ thống lưu vào database. Không hề có xử lý ràng buộc thời gian.</t>
+  </si>
+  <si>
+    <t>Khuyến nghị của AI đánh giá sai giá trị cốt lõi của phần mềm (Core Value). Báo cáo doanh thu (R05) hoàn toàn có thể xuất thủ công bằng lệnh SQL/Excel trong những tháng đầu. Ngược lại, nếu thiếu R06, bệnh nhân sẽ đến nhầm cơ sở khám, gây đổ vỡ hoàn toàn quy trình nghiệp vụ (Business Rule). Tôi đã sử dụng tư duy phân tích rủi ro để đảo ngược quyết định của AI: R06 thành Must Have, R05 thành Could Have.</t>
+  </si>
+  <si>
+    <t>AI mắc lỗi bỏ sót logic nghiệp vụ cơ bản (Logic Omission). Luồng của AI cho phép bệnh nhân đặt lịch lùi về ngày hôm qua (quá khứ). Tôi đã tự thiết kế lại luồng bằng cách bổ sung ràng buộc dữ liệu (Data Constraint) ở AC số 4: Hệ thống phải "disabled" (làm mờ) toàn bộ các ngày trong quá khứ và chỉ cho phép chọn Date &gt;= Today để ngăn chặn rác dữ liệu.</t>
+  </si>
+  <si>
+    <t>Phần 1a — Giải thích lý do R06 là Must Have (Bài tập 1).</t>
+  </si>
+  <si>
+    <t>Phần 3a — Acceptance Criteria số 4: Đặt lịch vào quá khứ (Bài tập 3).</t>
+  </si>
+  <si>
+    <t>Verification / Review</t>
+  </si>
+  <si>
+    <t>Document Inspection / Static Testing</t>
+  </si>
+  <si>
+    <t>Xác định loại hình kiểm thử (Verification hay Validation) cho Tình huống TH4: PM đọc và so sánh Business Requirements với Software Requirements.</t>
+  </si>
+  <si>
+    <t>"Trong tình huống PM so sánh 2 loại tài liệu để tìm chỗ dịch sai, đây là Verification hay Validation? Giải thích.</t>
+  </si>
+  <si>
+    <r>
+      <t>AI khẳng định đây là "Validation" với lý do: "Vì PM đang xem xét Business Requirements của khách hàng, tức là đang kiểm chứng với nhu AI bị nhầm lẫn khái niệm lý thuyết (Concept Confusion). Validation bắt buộc phải là hành động kiểm chứng phần mềm chạy thực tế với người dùng cuối. Việc PM ngồi đối chiếu tĩnh giữa 2 văn bản (Static Testing / Traceabi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>lity check) để tìm lỗi chuyển đổi thông tin hoàn toàn mang bản chất của Verification (Làm đúng tài liệu). Tôi đã bác bỏ AI và sửa lại thành Verification.cầu kinh doanh".</t>
+    </r>
+  </si>
+  <si>
+    <t>AI bị nhầm lẫn khái niệm lý thuyết (Concept Confusion). Validation bắt buộc phải là hành động kiểm chứng phần mềm chạy thực tế với người dùng cuối. Việc PM ngồi đối chiếu tĩnh giữa 2 văn bản (Static Testing / Traceability check) để tìm lỗi chuyển đổi thông tin hoàn toàn mang bản chất của Verification (Làm đúng tài liệu). Tôi đã bác bỏ AI và sửa lại thành Verification.</t>
+  </si>
+  <si>
+    <t>Phần 2a — Phân tích Tình huống TH4 (Bài tập 2).</t>
   </si>
 </sst>
 </file>
@@ -1102,7 +1303,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1177,6 +1378,13 @@
       <i/>
       <sz val="10"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1301,6 +1509,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1318,9 +1529,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1636,14 +1844,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
     </row>
     <row r="3" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
@@ -1852,42 +2060,42 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="20.6328125" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="31" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="32.6328125" customWidth="1"/>
-    <col min="6" max="6" width="35" customWidth="1"/>
-    <col min="7" max="7" width="84.6328125" customWidth="1"/>
+    <col min="4" max="4" width="40.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="88.08984375" customWidth="1"/>
+    <col min="7" max="7" width="119.08984375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
     </row>
     <row r="3" spans="1:8" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
@@ -2498,16 +2706,16 @@
       <c r="D26" s="20" t="s">
         <v>317</v>
       </c>
-      <c r="E26" s="28" t="s">
+      <c r="E26" s="20" t="s">
         <v>325</v>
       </c>
-      <c r="F26" s="28" t="s">
+      <c r="F26" s="20" t="s">
         <v>327</v>
       </c>
-      <c r="G26" s="28" t="s">
+      <c r="G26" s="20" t="s">
         <v>328</v>
       </c>
-      <c r="H26" s="28" t="s">
+      <c r="H26" s="20" t="s">
         <v>329</v>
       </c>
     </row>
@@ -2524,19 +2732,100 @@
       <c r="D27" s="20" t="s">
         <v>318</v>
       </c>
-      <c r="E27" s="28" t="s">
+      <c r="E27" s="20" t="s">
         <v>326</v>
       </c>
-      <c r="F27" s="28" t="s">
+      <c r="F27" s="20" t="s">
         <v>330</v>
       </c>
-      <c r="G27" s="28" t="s">
+      <c r="G27" s="20" t="s">
         <v>331</v>
       </c>
-      <c r="H27" s="28" t="s">
+      <c r="H27" s="20" t="s">
         <v>332</v>
       </c>
     </row>
+    <row r="28" spans="1:8" ht="55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="20">
+        <v>25</v>
+      </c>
+      <c r="B28" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>397</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>399</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>401</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>403</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>405</v>
+      </c>
+      <c r="H28" s="20" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="20">
+        <v>26</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>398</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>400</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>402</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>404</v>
+      </c>
+      <c r="G29" s="20" t="s">
+        <v>406</v>
+      </c>
+      <c r="H29" s="20" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="80.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="20">
+        <v>27</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>409</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="D30" s="20" t="s">
+        <v>411</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>412</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>413</v>
+      </c>
+      <c r="G30" s="29" t="s">
+        <v>414</v>
+      </c>
+      <c r="H30" s="29" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="51.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="32" spans="1:8" ht="59.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="33" ht="64.5" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
@@ -2548,11 +2837,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="1" max="1" width="39.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.08984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="53.453125" customWidth="1"/>
     <col min="4" max="4" width="84.453125" customWidth="1"/>
     <col min="5" max="5" width="38.36328125" customWidth="1"/>
@@ -2560,24 +2849,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
     </row>
     <row r="3" spans="1:6" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
@@ -2980,154 +3269,368 @@
       </c>
     </row>
     <row r="23" spans="1:6" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="28">
+      <c r="A23" s="20">
         <v>20</v>
       </c>
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="20" t="s">
         <v>333</v>
       </c>
-      <c r="C23" s="28" t="s">
+      <c r="C23" s="20" t="s">
         <v>337</v>
       </c>
-      <c r="D23" s="28" t="s">
+      <c r="D23" s="20" t="s">
         <v>341</v>
       </c>
-      <c r="E23" s="28" t="s">
+      <c r="E23" s="20" t="s">
         <v>343</v>
       </c>
-      <c r="F23" s="29" t="s">
+      <c r="F23" s="21" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="28">
+      <c r="A24" s="20">
         <v>21</v>
       </c>
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="20" t="s">
         <v>334</v>
       </c>
-      <c r="C24" s="28" t="s">
+      <c r="C24" s="20" t="s">
         <v>338</v>
       </c>
-      <c r="D24" s="28" t="s">
+      <c r="D24" s="20" t="s">
         <v>342</v>
       </c>
-      <c r="E24" s="28" t="s">
+      <c r="E24" s="20" t="s">
         <v>344</v>
       </c>
-      <c r="F24" s="29" t="s">
+      <c r="F24" s="21" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="90.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="28">
+      <c r="A25" s="20">
         <v>22</v>
       </c>
       <c r="B25" s="19" t="s">
         <v>335</v>
       </c>
-      <c r="C25" s="28" t="s">
+      <c r="C25" s="20" t="s">
         <v>339</v>
       </c>
-      <c r="D25" s="28" t="s">
+      <c r="D25" s="20" t="s">
         <v>347</v>
       </c>
-      <c r="E25" s="28" t="s">
+      <c r="E25" s="20" t="s">
         <v>349</v>
       </c>
-      <c r="F25" s="29" t="s">
+      <c r="F25" s="21" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="80" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="28">
+    <row r="26" spans="1:6" ht="90.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="20">
         <v>23</v>
       </c>
-      <c r="B26" s="29" t="s">
+      <c r="B26" s="19" t="s">
+        <v>353</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>354</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>357</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>359</v>
+      </c>
+      <c r="F26" s="21" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="90.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="20">
+        <v>24</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>355</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>356</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>358</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>361</v>
+      </c>
+      <c r="F27" s="21" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="80" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="20">
+        <v>25</v>
+      </c>
+      <c r="B28" s="21" t="s">
         <v>336</v>
       </c>
-      <c r="C26" s="28" t="s">
+      <c r="C28" s="20" t="s">
         <v>340</v>
       </c>
-      <c r="D26" s="28" t="s">
+      <c r="D28" s="20" t="s">
         <v>348</v>
       </c>
-      <c r="E26" s="28" t="s">
+      <c r="E28" s="20" t="s">
         <v>350</v>
       </c>
-      <c r="F26" s="29" t="s">
+      <c r="F28" s="21" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A27" s="1" t="s">
+    <row r="29" spans="1:6" ht="80" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="22">
+        <v>26</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>363</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>364</v>
+      </c>
+      <c r="D29" s="22" t="s">
+        <v>365</v>
+      </c>
+      <c r="E29" s="22" t="s">
+        <v>366</v>
+      </c>
+      <c r="F29" s="22" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="10" t="s">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B31" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C31" s="10" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A29" s="7" t="s">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B32" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C32" s="7" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A30" s="7" t="s">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B33" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C33" s="7" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A31" s="7" t="s">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B34" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C34" s="7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A32" s="7" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B35" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C35" s="7" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="7" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B36" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C36" s="7" t="s">
         <v>76</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="53.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="B37" s="20" t="s">
+        <v>368</v>
+      </c>
+      <c r="C37" s="20" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="B38" s="20" t="s">
+        <v>369</v>
+      </c>
+      <c r="C38" s="20" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>370</v>
+      </c>
+      <c r="C39" s="20" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="92.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="20" t="s">
+        <v>374</v>
+      </c>
+      <c r="B40" s="20" t="s">
+        <v>375</v>
+      </c>
+      <c r="C40" s="20" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="B41" s="20" t="s">
+        <v>376</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>379</v>
+      </c>
+      <c r="C42" s="20" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="65.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="20" t="s">
+        <v>333</v>
+      </c>
+      <c r="B43" s="20" t="s">
+        <v>381</v>
+      </c>
+      <c r="C43" s="20" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="64" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="B44" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="C44" s="20" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="64" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="20" t="s">
+        <v>335</v>
+      </c>
+      <c r="B45" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="C45" s="20" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="20" t="s">
+        <v>353</v>
+      </c>
+      <c r="B46" s="20" t="s">
+        <v>387</v>
+      </c>
+      <c r="C46" s="20" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="56.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="B47" s="20" t="s">
+        <v>388</v>
+      </c>
+      <c r="C47" s="20" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="60.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="B48" s="20" t="s">
+        <v>389</v>
+      </c>
+      <c r="C48" s="20" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="59.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="20" t="s">
+        <v>355</v>
+      </c>
+      <c r="B49" s="20" t="s">
+        <v>390</v>
+      </c>
+      <c r="C49" s="20" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="20" t="s">
+        <v>334</v>
+      </c>
+      <c r="B50" s="20" t="s">
+        <v>391</v>
+      </c>
+      <c r="C50" s="20" t="s">
+        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -3151,20 +3654,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
     </row>
     <row r="4" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
